--- a/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,10 +38,10 @@
     <t>P7-05</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KCL-1002</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>KCL-0002</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Đất san lấp</t>
+    <t>Đất san lấp / Cát san lấp</t>
   </si>
   <si>
     <t xml:space="preserve">14:40
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">15:45
@@ -184,7 +184,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">20:30
@@ -198,7 +198,7 @@
     <t>9</t>
   </si>
   <si>
-    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:30
@@ -210,9 +210,6 @@
   </si>
   <si>
     <t>10</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:08
@@ -1543,13 +1540,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>59</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F20" s="34">
         <v>-40.2</v>
@@ -1572,7 +1569,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1678,31 +1675,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1974,7 +1971,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1997,7 +1994,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>KCL-0002</t>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,13 +106,10 @@
 11/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">15:31
@@ -132,9 +129,6 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">16:10
 11/03/2026</t>
   </si>
@@ -160,7 +154,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:55
@@ -168,9 +162,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">19:00
@@ -250,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -326,11 +317,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
@@ -349,7 +335,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,22 +399,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5F3FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -529,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -609,17 +590,17 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -633,22 +614,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1249,24 +1221,24 @@
         <v>9.2</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-1.227</v>
@@ -1284,24 +1256,24 @@
         <v>9.06</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="14" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-7.72</v>
@@ -1319,24 +1291,24 @@
         <v>8.57</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="15">
         <v>-9.72</v>
@@ -1354,24 +1326,24 @@
         <v>5.45</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="20" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>44</v>
       </c>
       <c r="F15" s="18">
         <v>-17.9</v>
@@ -1389,24 +1361,24 @@
         <v>7.17</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F16" s="21">
         <v>-22.2</v>
@@ -1424,163 +1396,163 @@
         <v>7.06</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="24">
+      <c r="F17" s="21">
         <v>-26.2</v>
       </c>
-      <c r="G17" s="24">
+      <c r="G17" s="21">
         <v>-36.2</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="21">
         <v>1.33</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="21">
         <v>10</v>
       </c>
       <c r="J17" s="8">
         <v>7.5</v>
       </c>
-      <c r="K17" s="25" t="s">
-        <v>30</v>
+      <c r="K17" s="22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="F18" s="24">
+        <v>-36.2</v>
+      </c>
+      <c r="G18" s="24">
+        <v>-38.7</v>
+      </c>
+      <c r="H18" s="24">
+        <v>0.83</v>
+      </c>
+      <c r="I18" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="J18" s="27">
+        <v>3</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="29" t="s">
+      <c r="C19" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="D19" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="27">
-        <v>-36.2</v>
-      </c>
-      <c r="G18" s="27">
+      <c r="E19" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="28">
         <v>-38.7</v>
       </c>
-      <c r="H18" s="27">
-        <v>0.83</v>
-      </c>
-      <c r="I18" s="27">
-        <v>2.5</v>
-      </c>
-      <c r="J18" s="30">
+      <c r="G19" s="28">
+        <v>-40.2</v>
+      </c>
+      <c r="H19" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="I19" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="J19" s="27">
         <v>3</v>
       </c>
-      <c r="K18" s="28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+      <c r="K19" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="33" t="s">
+      <c r="E20" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="33" t="s">
+      <c r="F20" s="31">
+        <v>-40.2</v>
+      </c>
+      <c r="G20" s="31">
+        <v>-45.05</v>
+      </c>
+      <c r="H20" s="31">
+        <v>8.13</v>
+      </c>
+      <c r="I20" s="31">
+        <v>4.85</v>
+      </c>
+      <c r="J20" s="34">
+        <v>0.6</v>
+      </c>
+      <c r="K20" s="32" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="31">
-        <v>-38.7</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-40.2</v>
-      </c>
-      <c r="H19" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="I19" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="J19" s="30">
-        <v>3</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-40.2</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-45.05</v>
-      </c>
-      <c r="H20" s="34">
-        <v>8.13</v>
-      </c>
-      <c r="I20" s="34">
-        <v>4.85</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.6</v>
-      </c>
-      <c r="K20" s="35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1662,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1675,31 +1647,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1739,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1768,7 +1740,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1797,7 +1769,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1826,7 +1798,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1855,25 +1827,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="21">
         <v>-22.2</v>
       </c>
       <c r="F7" s="21">
-        <v>-26.2</v>
+        <v>-36.2</v>
       </c>
       <c r="G7" s="21">
-        <v>0.57</v>
+        <v>1.9</v>
       </c>
       <c r="H7" s="21">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I7" s="8">
-        <v>7.06</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1884,53 +1856,53 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-26.2</v>
+        <v>-36.2</v>
       </c>
       <c r="F8" s="24">
-        <v>-36.2</v>
+        <v>-38.7</v>
       </c>
       <c r="G8" s="24">
-        <v>1.33</v>
+        <v>0.83</v>
       </c>
       <c r="H8" s="24">
-        <v>10</v>
-      </c>
-      <c r="I8" s="8">
-        <v>7.5</v>
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="27">
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="27">
+      <c r="C9" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="27">
-        <v>-36.2</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="28">
         <v>-38.7</v>
       </c>
-      <c r="G9" s="27">
-        <v>0.83</v>
-      </c>
-      <c r="H9" s="27">
-        <v>2.5</v>
-      </c>
-      <c r="I9" s="30">
+      <c r="F9" s="28">
+        <v>-40.2</v>
+      </c>
+      <c r="G9" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="28">
+        <v>1.5</v>
+      </c>
+      <c r="I9" s="27">
         <v>3</v>
       </c>
     </row>
@@ -1942,82 +1914,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-38.7</v>
+        <v>-40.2</v>
       </c>
       <c r="F10" s="31">
-        <v>-40.2</v>
+        <v>-45.05</v>
       </c>
       <c r="G10" s="31">
-        <v>0.5</v>
+        <v>8.13</v>
       </c>
       <c r="H10" s="31">
-        <v>1.5</v>
-      </c>
-      <c r="I10" s="30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+        <v>4.85</v>
+      </c>
+      <c r="I10" s="34">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="37">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-40.2</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37">
         <v>-45.05</v>
       </c>
-      <c r="G11" s="34">
-        <v>8.13</v>
-      </c>
-      <c r="H11" s="34">
-        <v>4.85</v>
+      <c r="G11" s="37">
+        <v>14.55</v>
+      </c>
+      <c r="H11" s="37">
+        <v>45.05</v>
       </c>
       <c r="I11" s="37">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="40">
-        <v>10</v>
-      </c>
-      <c r="E12" s="40">
-        <v>0</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-45.05</v>
-      </c>
-      <c r="G12" s="40">
-        <v>14.55</v>
-      </c>
-      <c r="H12" s="40">
-        <v>45.05</v>
-      </c>
-      <c r="I12" s="40">
         <v>3.1</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
+++ b/SGC-CKN/Excel/d4fee85e-9d57-473e-805f-e24ed08bd8fe_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-05_D800_12-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0004</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">14:48
 11/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1221,24 +1224,24 @@
         <v>9.2</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-1.227</v>
@@ -1256,24 +1259,24 @@
         <v>9.06</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="12">
         <v>-7.72</v>
@@ -1291,24 +1294,24 @@
         <v>8.57</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="15">
         <v>-9.72</v>
@@ -1326,24 +1329,24 @@
         <v>5.45</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="18">
         <v>-17.9</v>
@@ -1361,24 +1364,24 @@
         <v>7.17</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="21">
         <v>-22.2</v>
@@ -1396,24 +1399,24 @@
         <v>7.06</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="21">
         <v>-26.2</v>
@@ -1431,24 +1434,24 @@
         <v>7.5</v>
       </c>
       <c r="K17" s="22" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="24">
         <v>-36.2</v>
@@ -1466,24 +1469,24 @@
         <v>3</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="28">
         <v>-38.7</v>
@@ -1501,24 +1504,24 @@
         <v>3</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" s="31">
         <v>-40.2</v>
@@ -1536,12 +1539,12 @@
         <v>0.6</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="35" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="35"/>
       <c r="C23" s="35"/>
@@ -1647,31 +1650,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1711,7 +1714,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1740,7 +1743,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="12">
         <v>1</v>
@@ -1769,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1798,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1827,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="21">
         <v>2</v>
@@ -1856,7 +1859,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -1885,7 +1888,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1914,7 +1917,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1937,13 +1940,13 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D11" s="37">
         <v>10</v>
